--- a/aula12/cadastro_alunos.xlsx
+++ b/aula12/cadastro_alunos.xlsx
@@ -443,7 +443,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
